--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67602_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67602_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R96d1f9129f474edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R413e55b50d9d430d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,51 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3723</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67602_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67602_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R413e55b50d9d430d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfb96f08536594d7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,816 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3723</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3723</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4799</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3365</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4799</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4799</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5516</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6913</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1931</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3365</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0856</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9064</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0856</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1931</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8383</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8024</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>17/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3723</x:v>
+        <x:v>      1.2290</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0892</x:v>
+        <x:v>      1.6232</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9100</x:v>
+        <x:v>      1.7666</x:v>
       </x:c>
     </x:row>
     <x:row>
